--- a/meta_dados/escolaridade_br_22_total.xlsx
+++ b/meta_dados/escolaridade_br_22_total.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cecília Barbosa\Documents\000000_dados\ciencia-dados-\meta_dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA0253E-D429-4DE5-9397-CCAC02AC0B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A81365D-F294-4B64-94ED-CF62CDC8692B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
-  <si>
-    <t>Brasil</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Rondônia</t>
   </si>
@@ -526,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -538,13 +535,13 @@
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -552,27 +549,27 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>73149578</v>
+        <v>646097</v>
       </c>
       <c r="C2">
-        <v>55305618</v>
+        <v>348066</v>
       </c>
       <c r="D2">
-        <v>25854291</v>
+        <v>164632</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>646097</v>
+        <v>296474</v>
       </c>
       <c r="C3">
-        <v>348066</v>
+        <v>179961</v>
       </c>
       <c r="D3">
-        <v>164632</v>
+        <v>84300</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -580,13 +577,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>296474</v>
+        <v>1224993</v>
       </c>
       <c r="C4">
-        <v>179961</v>
+        <v>1073286</v>
       </c>
       <c r="D4">
-        <v>84300</v>
+        <v>342566</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -594,13 +591,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1224993</v>
+        <v>179876</v>
       </c>
       <c r="C5">
-        <v>1073286</v>
+        <v>168642</v>
       </c>
       <c r="D5">
-        <v>342566</v>
+        <v>67045</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -608,13 +605,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>179876</v>
+        <v>3207626</v>
       </c>
       <c r="C6">
-        <v>168642</v>
+        <v>1874741</v>
       </c>
       <c r="D6">
-        <v>67045</v>
+        <v>601096</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -622,13 +619,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>3207626</v>
+        <v>217908</v>
       </c>
       <c r="C7">
-        <v>1874741</v>
+        <v>187665</v>
       </c>
       <c r="D7">
-        <v>601096</v>
+        <v>89191</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -636,13 +633,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>217908</v>
+        <v>513562</v>
       </c>
       <c r="C8">
-        <v>187665</v>
+        <v>394849</v>
       </c>
       <c r="D8">
-        <v>89191</v>
+        <v>176336</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -650,13 +647,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>513562</v>
+        <v>2678343</v>
       </c>
       <c r="C9">
-        <v>394849</v>
+        <v>1608640</v>
       </c>
       <c r="D9">
-        <v>176336</v>
+        <v>468681</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -664,13 +661,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>2678343</v>
+        <v>1421076</v>
       </c>
       <c r="C10">
-        <v>1608640</v>
+        <v>706287</v>
       </c>
       <c r="D10">
-        <v>468681</v>
+        <v>304955</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -678,13 +675,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1421076</v>
+        <v>3549426</v>
       </c>
       <c r="C11">
-        <v>706287</v>
+        <v>2290925</v>
       </c>
       <c r="D11">
-        <v>304955</v>
+        <v>759303</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -692,13 +689,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>3549426</v>
+        <v>1357806</v>
       </c>
       <c r="C12">
-        <v>2290925</v>
+        <v>800681</v>
       </c>
       <c r="D12">
-        <v>759303</v>
+        <v>339913</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -706,13 +703,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>1357806</v>
+        <v>1680839</v>
       </c>
       <c r="C13">
-        <v>800681</v>
+        <v>897675</v>
       </c>
       <c r="D13">
-        <v>339913</v>
+        <v>390742</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -720,13 +717,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>1680839</v>
+        <v>3529336</v>
       </c>
       <c r="C14">
-        <v>897675</v>
+        <v>2372798</v>
       </c>
       <c r="D14">
-        <v>390742</v>
+        <v>852481</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -734,13 +731,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>3529336</v>
+        <v>1323710</v>
       </c>
       <c r="C15">
-        <v>2372798</v>
+        <v>669520</v>
       </c>
       <c r="D15">
-        <v>852481</v>
+        <v>267996</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -748,13 +745,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>1323710</v>
+        <v>896104</v>
       </c>
       <c r="C16">
-        <v>669520</v>
+        <v>520086</v>
       </c>
       <c r="D16">
-        <v>267996</v>
+        <v>218255</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -762,13 +759,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>896104</v>
+        <v>5879900</v>
       </c>
       <c r="C17">
-        <v>520086</v>
+        <v>3616133</v>
       </c>
       <c r="D17">
-        <v>218255</v>
+        <v>1146608</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -776,13 +773,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>5879900</v>
+        <v>7922097</v>
       </c>
       <c r="C18">
-        <v>3616133</v>
+        <v>5483064</v>
       </c>
       <c r="D18">
-        <v>1146608</v>
+        <v>2615434</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -790,13 +787,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>7922097</v>
+        <v>1396653</v>
       </c>
       <c r="C19">
-        <v>5483064</v>
+        <v>1051848</v>
       </c>
       <c r="D19">
-        <v>2615434</v>
+        <v>491101</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -804,13 +801,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>1396653</v>
+        <v>5306787</v>
       </c>
       <c r="C20">
-        <v>1051848</v>
+        <v>5034405</v>
       </c>
       <c r="D20">
-        <v>491101</v>
+        <v>2243707</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -818,13 +815,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>5306787</v>
+        <v>13551980</v>
       </c>
       <c r="C21">
-        <v>5034405</v>
+        <v>13692410</v>
       </c>
       <c r="D21">
-        <v>2243707</v>
+        <v>7478587</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -832,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>13551980</v>
+        <v>4027128</v>
       </c>
       <c r="C22">
-        <v>13692410</v>
+        <v>3075397</v>
       </c>
       <c r="D22">
-        <v>7478587</v>
+        <v>1687930</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -846,13 +843,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>4027128</v>
+        <v>2607840</v>
       </c>
       <c r="C23">
-        <v>3075397</v>
+        <v>2134682</v>
       </c>
       <c r="D23">
-        <v>1687930</v>
+        <v>1162515</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -860,13 +857,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>2607840</v>
+        <v>4225103</v>
       </c>
       <c r="C24">
-        <v>2134682</v>
+        <v>2862843</v>
       </c>
       <c r="D24">
-        <v>1162515</v>
+        <v>1488416</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -874,13 +871,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>4225103</v>
+        <v>1027451</v>
       </c>
       <c r="C25">
-        <v>2862843</v>
+        <v>637360</v>
       </c>
       <c r="D25">
-        <v>1488416</v>
+        <v>366249</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -888,13 +885,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>1027451</v>
+        <v>1321862</v>
       </c>
       <c r="C26">
-        <v>637360</v>
+        <v>893925</v>
       </c>
       <c r="D26">
-        <v>366249</v>
+        <v>450264</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,13 +899,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>1321862</v>
+        <v>2522991</v>
       </c>
       <c r="C27">
-        <v>893925</v>
+        <v>1921726</v>
       </c>
       <c r="D27">
-        <v>450264</v>
+        <v>879270</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -916,26 +913,12 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>2522991</v>
+        <v>636609</v>
       </c>
       <c r="C28">
-        <v>1921726</v>
+        <v>808005</v>
       </c>
       <c r="D28">
-        <v>879270</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1">
-        <v>636609</v>
-      </c>
-      <c r="C29">
-        <v>808005</v>
-      </c>
-      <c r="D29">
         <v>716719</v>
       </c>
     </row>
@@ -953,19 +936,19 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3"/>
     </row>
@@ -975,64 +958,64 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
         <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
-      </c>
-      <c r="B10" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
         <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/meta_dados/escolaridade_br_22_total.xlsx
+++ b/meta_dados/escolaridade_br_22_total.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cecília Barbosa\Documents\000000_dados\ciencia-dados-\meta_dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A81365D-F294-4B64-94ED-CF62CDC8692B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E98CAB-B4C7-49C0-994F-BDB1F893952E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
